--- a/Configs/GameConfig/Datas/fg/#SiegeCategory-攻城建筑类别.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeCategory-攻城建筑类别.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +753,19 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>purify</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#SiegeCategory-攻城建筑类别.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeCategory-攻城建筑类别.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>攻城目标类别:core / power / signal / defense / listening(other 不用登记)</t>
+          <t>攻城目标类别:core / power / signal / defense / listening / purify(净化塔,FG10-RAID-01;other 不用登记)</t>
         </is>
       </c>
     </row>
